--- a/labs/day3/d3_grade_banding.xlsx
+++ b/labs/day3/d3_grade_banding.xlsx
@@ -518,7 +518,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3일차 실습 B-1 — S/A/B/C 등급 매칭 시트</t>
+          <t>3일차 실습 B-1 — S/A/B/C 등급 매칭 시트(빈 양식 · 선택) — 수업 시간에는 완성본 d3_grade_banding_example.xlsx를 쓰고, 이 양식은 엑셀로 직접 해 보고 싶을 때(수업 뒤) 쓴다</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>⑥ pred 시트(buyer_id · ref_date · pd_30d · grade)를 파일 › 다른 이름으로 저장 › CSV UTF-8(쉼표로 분리)로 workbench/day3/outputs/d3_grade_excel.csv에 저장한다. 최종 d3_end_scored.csv(6열)는 Claude Code가 같은 규칙으로 만들고 이 파일과 견준다.</t>
+          <t>⑥ 결과가 완성본(labs/day3/d3_grade_banding_example.xlsx)의 등급 분포 · 단조성 표와 같은지 본다. 다르면 t 값 · 붙여 넣은 행 수 · 수식 순서(C부터 검사)를 확인한다.</t>
         </is>
       </c>
     </row>
